--- a/outputs/ranker/baseline/before_after_ranking_comparison.xlsx
+++ b/outputs/ranker/baseline/before_after_ranking_comparison.xlsx
@@ -537,13 +537,13 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>82.57122999999999</v>
+        <v>83.85393999999999</v>
       </c>
       <c r="J2">
-        <v>92.12506713759549</v>
+        <v>92.08215433577567</v>
       </c>
       <c r="K2">
-        <v>0.6681571428571429</v>
+        <v>0.6684142857142857</v>
       </c>
       <c r="L2">
         <v>92.202</v>
@@ -578,31 +578,31 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>76.09411999999999</v>
+        <v>75.5758</v>
       </c>
       <c r="J3">
-        <v>50.03060684747887</v>
+        <v>48.85282295672324</v>
       </c>
       <c r="K3">
-        <v>0.2212852953210594</v>
+        <v>0.1179641005309339</v>
       </c>
       <c r="L3">
-        <v>50.049</v>
+        <v>49.02</v>
       </c>
       <c r="M3">
-        <v>38.235</v>
+        <v>35.294</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -631,34 +631,34 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>75.14403999999999</v>
+        <v>75.72197</v>
       </c>
       <c r="J4">
-        <v>46.96644294363724</v>
+        <v>48.04866295692377</v>
       </c>
       <c r="K4">
-        <v>0.06889635435837743</v>
+        <v>0.1724980856091174</v>
       </c>
       <c r="L4">
-        <v>46.961</v>
+        <v>47.854</v>
       </c>
       <c r="M4">
         <v>29.412</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="O4">
         <v>83.333</v>
@@ -684,25 +684,25 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
-        <v>75.71343999999999</v>
+        <v>75.23186</v>
       </c>
       <c r="J5">
-        <v>46.85639184001016</v>
+        <v>46.94281661630287</v>
       </c>
       <c r="K5">
-        <v>0.1646994769048391</v>
+        <v>0.05754202607881254</v>
       </c>
       <c r="L5">
         <v>46.824</v>
@@ -737,7 +737,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -749,22 +749,22 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>76.05423999999999</v>
+        <v>76.50287</v>
       </c>
       <c r="J6">
-        <v>43.7934912312782</v>
+        <v>46.66154313427446</v>
       </c>
       <c r="K6">
-        <v>0.2519774753419622</v>
+        <v>0.2947616366154081</v>
       </c>
       <c r="L6">
-        <v>43.736</v>
+        <v>46.688</v>
       </c>
       <c r="M6">
-        <v>17.647</v>
+        <v>23.529</v>
       </c>
       <c r="N6">
-        <v>3.571</v>
+        <v>7.143</v>
       </c>
       <c r="O6">
         <v>83.333</v>
